--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -622,12 +622,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -649,12 +649,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -676,12 +676,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -703,12 +703,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -730,12 +730,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -757,12 +757,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -784,12 +784,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -811,12 +811,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -838,12 +838,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -865,12 +865,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -892,83 +892,110 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>1951000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>232733.62</t>
+          <t>1951000</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>213910</t>
+          <t>232733.62</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>245576</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>18823.62</t>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>-12842.38</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/26 15:30:53</t>
+          <t>08/27 16:33:14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>266000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>31666.67</t>
+          <t>16666.67</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/23 09:56:14</t>
+          <t>08/26 15:30:53</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>266000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,12 +137,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>31666.67</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>马书文</t>
+          <t/>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/12 14:48:22</t>
+          <t>08/23 09:56:14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,17 +174,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>姚治文</t>
+          <t>马书文</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/11 14:11:24</t>
+          <t>08/12 14:48:22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,12 +221,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10843.37</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>姚治文</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/07 13:37:02</t>
+          <t>08/11 14:11:24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,17 +263,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>10843.37</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/04 13:42:31</t>
+          <t>08/07 13:37:02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/27 15:17:33</t>
+          <t>08/04 13:42:31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,17 +342,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10714.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/27 11:23:18</t>
+          <t>07/27 15:17:33</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>215000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,22 +384,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>25903.61</t>
+          <t>10714.29</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/24 11:11:31</t>
+          <t>07/27 11:23:18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>215000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,17 +431,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>25903.61</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>卢华</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/15 13:16:56</t>
+          <t>07/24 11:11:31</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,22 +468,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>邓迎春</t>
+          <t>卢华</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,166 +495,181 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>07/15 13:16:56</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>10588.24</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>邓迎春</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>07/07 10:57:55</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>58823.53</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>张黎</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -676,12 +691,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -703,12 +718,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -730,12 +745,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -757,12 +772,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -784,12 +799,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -811,12 +826,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -838,12 +853,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -865,12 +880,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -880,7 +895,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -892,12 +907,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -919,83 +934,110 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>1951000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>232733.62</t>
+          <t>2091000</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>245576</t>
+          <t>249400.29</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>245576</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>-12842.38</t>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>3824.29</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -664,12 +664,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -691,12 +691,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -718,12 +718,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -745,12 +745,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -772,12 +772,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -799,12 +799,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -826,12 +826,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -853,12 +853,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -880,12 +880,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -907,12 +907,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -934,12 +934,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -961,83 +961,110 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2091000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>249400.29</t>
+          <t>2091000</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>245576</t>
+          <t>249400.29</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>262242</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>3824.29</t>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>-12841.71</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/27 16:33:14</t>
+          <t>08/28 11:17:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16666.67</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/26 15:30:53</t>
+          <t>08/27 16:33:14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>266000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>31666.67</t>
+          <t>16666.67</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/23 09:56:14</t>
+          <t>08/26 15:30:53</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>266000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,12 +179,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>31666.67</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>马书文</t>
+          <t/>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/12 14:48:22</t>
+          <t>08/23 09:56:14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,17 +216,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>姚治文</t>
+          <t>马书文</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/11 14:11:24</t>
+          <t>08/12 14:48:22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,12 +263,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10843.37</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>姚治文</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/07 13:37:02</t>
+          <t>08/11 14:11:24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,17 +305,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>10843.37</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/04 13:42:31</t>
+          <t>08/07 13:37:02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/27 15:17:33</t>
+          <t>08/04 13:42:31</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,17 +384,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10714.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/27 11:23:18</t>
+          <t>07/27 15:17:33</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>215000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,22 +426,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>25903.61</t>
+          <t>10714.29</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/24 11:11:31</t>
+          <t>07/27 11:23:18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>215000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,17 +473,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>25903.61</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>卢华</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/15 13:16:56</t>
+          <t>07/24 11:11:31</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,22 +510,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>邓迎春</t>
+          <t>卢华</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,166 +537,181 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>07/15 13:16:56</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>10588.24</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>邓迎春</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>07/07 10:57:55</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>58823.53</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>张黎</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -718,12 +733,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -745,12 +760,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -772,12 +787,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -799,12 +814,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -826,12 +841,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -853,12 +868,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -880,12 +895,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -907,12 +922,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -934,12 +949,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -949,7 +964,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -961,12 +976,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -988,83 +1003,110 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2091000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>249400.29</t>
+          <t>2141000</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>262242</t>
+          <t>255352.67</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>262242</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>-12841.71</t>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>-6889.33</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -706,12 +706,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -733,12 +733,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -760,12 +760,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -787,12 +787,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -814,12 +814,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -841,12 +841,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -868,12 +868,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -895,12 +895,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -922,12 +922,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -949,12 +949,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -976,12 +976,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1003,12 +1003,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1030,83 +1030,110 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2141000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>255352.67</t>
+          <t>2141000</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>262242</t>
+          <t>255352.67</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>262630</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>-6889.33</t>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>-7277.33</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -706,12 +706,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -733,12 +733,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -760,12 +760,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -787,12 +787,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -814,12 +814,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -841,12 +841,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -868,12 +868,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -895,12 +895,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -922,12 +922,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -949,12 +949,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -976,12 +976,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1003,12 +1003,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1030,12 +1030,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1057,83 +1057,110 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2141000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>255352.67</t>
+          <t>2141000</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>262630</t>
+          <t>255352.67</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>268194</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>-7277.33</t>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>-12841.33</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/28 11:17:30</t>
+          <t>08/30 10:19:15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,12 +95,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t/>
+          <t>胡琪斌</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/27 16:33:14</t>
+          <t>08/28 11:17:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16666.67</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/26 15:30:53</t>
+          <t>08/27 16:33:14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>266000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>31666.67</t>
+          <t>16666.67</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/23 09:56:14</t>
+          <t>08/26 15:30:53</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>266000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,12 +221,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>31666.67</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>马书文</t>
+          <t/>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/12 14:48:22</t>
+          <t>08/23 09:56:14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,17 +258,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>姚治文</t>
+          <t>马书文</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/11 14:11:24</t>
+          <t>08/12 14:48:22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,12 +305,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10843.37</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>姚治文</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/07 13:37:02</t>
+          <t>08/11 14:11:24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,17 +347,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>10843.37</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/04 13:42:31</t>
+          <t>08/07 13:37:02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/27 15:17:33</t>
+          <t>08/04 13:42:31</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,17 +426,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10714.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/27 11:23:18</t>
+          <t>07/27 15:17:33</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>215000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,22 +468,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>25903.61</t>
+          <t>10714.29</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/24 11:11:31</t>
+          <t>07/27 11:23:18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>215000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,17 +515,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>25903.61</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>卢华</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/15 13:16:56</t>
+          <t>07/24 11:11:31</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,22 +552,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>邓迎春</t>
+          <t>卢华</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,166 +579,181 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>07/15 13:16:56</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>10588.24</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>邓迎春</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>07/07 10:57:55</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>58823.53</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>张黎</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -760,12 +775,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -775,7 +790,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -787,12 +802,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -814,12 +829,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -841,12 +856,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -868,12 +883,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -895,12 +910,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -922,12 +937,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -949,12 +964,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -976,12 +991,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1003,12 +1018,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1030,12 +1045,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1045,7 +1060,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1057,12 +1072,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1084,83 +1099,110 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2141000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>255352.67</t>
+          <t>2241000</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>268194</t>
+          <t>267257.43</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>268194</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>-12841.33</t>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>-936.57</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -748,12 +748,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -775,12 +775,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -802,12 +802,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -829,12 +829,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -856,12 +856,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -883,12 +883,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -910,12 +910,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -937,12 +937,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -964,12 +964,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -991,12 +991,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1018,12 +1018,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1045,12 +1045,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1072,12 +1072,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1099,12 +1099,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1126,83 +1126,110 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2241000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>267257.43</t>
+          <t>2241000</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>268194</t>
+          <t>267257.43</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>280098</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>-936.57</t>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>-12840.57</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/30 10:19:15</t>
+          <t>09/02 15:56:24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,22 +90,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>9036.14</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>胡琪斌</t>
+          <t>许定勇</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/28 11:17:30</t>
+          <t>08/30 10:19:15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,12 +137,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t/>
+          <t>胡琪斌</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/27 16:33:14</t>
+          <t>08/28 11:17:30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16666.67</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/26 15:30:53</t>
+          <t>08/27 16:33:14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>266000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>31666.67</t>
+          <t>16666.67</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/23 09:56:14</t>
+          <t>08/26 15:30:53</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>266000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,12 +263,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>31666.67</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>马书文</t>
+          <t/>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/12 14:48:22</t>
+          <t>08/23 09:56:14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,17 +300,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>姚治文</t>
+          <t>马书文</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/11 14:11:24</t>
+          <t>08/12 14:48:22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,12 +347,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10843.37</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>姚治文</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/07 13:37:02</t>
+          <t>08/11 14:11:24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,17 +389,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>10843.37</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/04 13:42:31</t>
+          <t>08/07 13:37:02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/27 15:17:33</t>
+          <t>08/04 13:42:31</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,17 +468,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10714.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/27 11:23:18</t>
+          <t>07/27 15:17:33</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>215000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,22 +510,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>25903.61</t>
+          <t>10714.29</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/24 11:11:31</t>
+          <t>07/27 11:23:18</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>215000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,17 +557,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>25903.61</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>卢华</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/15 13:16:56</t>
+          <t>07/24 11:11:31</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,22 +594,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>邓迎春</t>
+          <t>卢华</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,166 +621,181 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>07/15 13:16:56</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>10588.24</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>邓迎春</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>07/07 10:57:55</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>58823.53</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>张黎</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -802,12 +817,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -829,12 +844,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -844,7 +859,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -856,12 +871,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -883,12 +898,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -910,12 +925,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -937,12 +952,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -964,12 +979,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -991,12 +1006,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1018,12 +1033,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1045,12 +1060,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1072,12 +1087,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1099,12 +1114,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1114,7 +1129,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1126,12 +1141,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1153,83 +1168,110 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2241000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>267257.43</t>
+          <t>2316000</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>280098</t>
+          <t>276293.58</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>280098</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>-12840.57</t>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>-3804.42</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -790,12 +790,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -817,12 +817,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -844,12 +844,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -871,12 +871,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -898,12 +898,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -925,12 +925,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -952,12 +952,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -979,12 +979,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1006,12 +1006,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1033,12 +1033,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1060,12 +1060,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1087,12 +1087,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1114,12 +1114,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1141,12 +1141,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1168,12 +1168,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1195,83 +1195,110 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2316000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>276293.58</t>
+          <t>2316000</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>280098</t>
+          <t>276293.58</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>281098</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>-3804.42</t>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>-4804.42</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -790,12 +790,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -817,12 +817,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -844,12 +844,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -871,12 +871,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -898,12 +898,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -925,12 +925,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -952,12 +952,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -979,12 +979,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1006,12 +1006,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1033,12 +1033,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1060,12 +1060,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1087,12 +1087,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1114,12 +1114,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1141,12 +1141,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1168,12 +1168,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1195,12 +1195,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1222,83 +1222,110 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="43"/>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2316000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>276293.58</t>
+          <t>2316000</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>281098</t>
+          <t>276293.58</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>289134</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>-4804.42</t>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>-12840.42</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/02 15:56:24</t>
+          <t>09/03 12:12:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>95000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,22 +90,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9036.14</t>
+          <t>11309.52</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>许定勇</t>
+          <t>毕春丽</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/30 10:19:15</t>
+          <t>09/02 15:56:24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,22 +132,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>9036.14</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>胡琪斌</t>
+          <t>许定勇</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/28 11:17:30</t>
+          <t>08/30 10:19:15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,12 +179,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t/>
+          <t>胡琪斌</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/27 16:33:14</t>
+          <t>08/28 11:17:30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16666.67</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/26 15:30:53</t>
+          <t>08/27 16:33:14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>266000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>31666.67</t>
+          <t>16666.67</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/23 09:56:14</t>
+          <t>08/26 15:30:53</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>266000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,12 +305,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>31666.67</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>马书文</t>
+          <t/>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/12 14:48:22</t>
+          <t>08/23 09:56:14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,17 +342,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>姚治文</t>
+          <t>马书文</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/11 14:11:24</t>
+          <t>08/12 14:48:22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,12 +389,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10843.37</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>姚治文</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/07 13:37:02</t>
+          <t>08/11 14:11:24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,17 +431,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>10843.37</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/04 13:42:31</t>
+          <t>08/07 13:37:02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/27 15:17:33</t>
+          <t>08/04 13:42:31</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,17 +510,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>10714.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/27 11:23:18</t>
+          <t>07/27 15:17:33</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>215000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,22 +552,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>25903.61</t>
+          <t>10714.29</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/24 11:11:31</t>
+          <t>07/27 11:23:18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>215000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,17 +599,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>25903.61</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>卢华</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/15 13:16:56</t>
+          <t>07/24 11:11:31</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,22 +636,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>邓迎春</t>
+          <t>卢华</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,166 +663,181 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>07/15 13:16:56</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>10588.24</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>邓迎春</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>07/07 10:57:55</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>58823.53</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>张黎</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -844,12 +859,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -859,7 +874,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -871,12 +886,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -898,12 +913,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -925,12 +940,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -940,7 +955,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -952,12 +967,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -979,12 +994,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1006,12 +1021,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1033,12 +1048,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1060,12 +1075,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1087,12 +1102,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1114,12 +1129,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1141,12 +1156,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1168,12 +1183,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1195,12 +1210,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1210,7 +1225,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1222,12 +1237,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1249,83 +1264,110 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2316000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>276293.58</t>
+          <t>2411000</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>289134</t>
+          <t>287603.1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>289134</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>-12840.42</t>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>-1530.9</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/03 12:12:00</t>
+          <t>09/03 14:05:04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>95000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,22 +90,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11309.52</t>
+          <t>11627.91</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>毕春丽</t>
+          <t>贾凌</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/02 15:56:24</t>
+          <t>09/03 12:12:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>95000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,22 +132,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>9036.14</t>
+          <t>11309.52</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>许定勇</t>
+          <t>毕春丽</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/30 10:19:15</t>
+          <t>09/02 15:56:24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,22 +174,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>9036.14</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>胡琪斌</t>
+          <t>许定勇</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/28 11:17:30</t>
+          <t>08/30 10:19:15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,12 +221,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t/>
+          <t>胡琪斌</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/27 16:33:14</t>
+          <t>08/28 11:17:30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>16666.67</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/26 15:30:53</t>
+          <t>08/27 16:33:14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>266000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>31666.67</t>
+          <t>16666.67</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/23 09:56:14</t>
+          <t>08/26 15:30:53</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>266000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,12 +347,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>31666.67</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>马书文</t>
+          <t/>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/12 14:48:22</t>
+          <t>08/23 09:56:14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,17 +384,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>姚治文</t>
+          <t>马书文</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/11 14:11:24</t>
+          <t>08/12 14:48:22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,12 +431,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10843.37</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>姚治文</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/07 13:37:02</t>
+          <t>08/11 14:11:24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,17 +473,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>10843.37</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/04 13:42:31</t>
+          <t>08/07 13:37:02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/27 15:17:33</t>
+          <t>08/04 13:42:31</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,17 +552,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10714.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/27 11:23:18</t>
+          <t>07/27 15:17:33</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>215000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,22 +594,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>25903.61</t>
+          <t>10714.29</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/24 11:11:31</t>
+          <t>07/27 11:23:18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>215000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,17 +641,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>25903.61</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>卢华</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/15 13:16:56</t>
+          <t>07/24 11:11:31</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,22 +678,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>邓迎春</t>
+          <t>卢华</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,166 +705,181 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>07/15 13:16:56</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>10588.24</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>邓迎春</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>07/07 10:57:55</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>58823.53</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>张黎</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -886,12 +901,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -901,7 +916,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -913,12 +928,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -940,12 +955,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -967,12 +982,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -982,7 +997,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -994,12 +1009,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1021,12 +1036,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1048,12 +1063,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1075,12 +1090,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1102,12 +1117,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1129,12 +1144,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1156,12 +1171,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1183,12 +1198,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1210,12 +1225,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1237,12 +1252,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1252,7 +1267,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1264,12 +1279,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1291,83 +1306,110 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="45"/>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2411000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>287603.1</t>
+          <t>2511000</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>289134</t>
+          <t>299231.01</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>289134</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>-1530.9</t>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>10097.01</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -874,12 +874,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>09/03 14:06:24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -901,12 +901,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -928,12 +928,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -955,12 +955,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -982,12 +982,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1036,12 +1036,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1063,12 +1063,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1090,12 +1090,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1117,12 +1117,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1144,12 +1144,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1171,12 +1171,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1198,12 +1198,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1225,12 +1225,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1252,12 +1252,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1279,12 +1279,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1306,12 +1306,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1333,83 +1333,110 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="46"/>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2511000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>299231.01</t>
+          <t>2511000</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>289134</t>
+          <t>299231.01</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>290134</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>10097.01</t>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>9097.01</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -874,12 +874,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/03 14:06:24</t>
+          <t>09/03 15:50:47</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -901,12 +901,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>09/03 14:06:24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -928,12 +928,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -955,12 +955,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -982,12 +982,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1036,12 +1036,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1063,12 +1063,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1090,12 +1090,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1117,12 +1117,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1144,12 +1144,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1171,12 +1171,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1198,12 +1198,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1225,12 +1225,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1252,12 +1252,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1279,12 +1279,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1306,12 +1306,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1333,12 +1333,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1360,83 +1360,110 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="47"/>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2511000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>299231.01</t>
+          <t>2511000</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>290134</t>
+          <t>299231.01</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>312071</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>9097.01</t>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>-12839.99</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/03 14:05:04</t>
+          <t>09/04 17:04:18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,22 +90,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11627.91</t>
+          <t>8536.59</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>贾凌</t>
+          <t>唐志刚</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/03 12:12:00</t>
+          <t>09/03 14:05:04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>95000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,22 +132,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11309.52</t>
+          <t>11627.91</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>毕春丽</t>
+          <t>贾凌</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/02 15:56:24</t>
+          <t>09/03 12:12:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>95000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,22 +174,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>9036.14</t>
+          <t>11309.52</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>许定勇</t>
+          <t>毕春丽</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/30 10:19:15</t>
+          <t>09/02 15:56:24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,22 +216,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>9036.14</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>胡琪斌</t>
+          <t>许定勇</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/28 11:17:30</t>
+          <t>08/30 10:19:15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,12 +263,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t/>
+          <t>胡琪斌</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/27 16:33:14</t>
+          <t>08/28 11:17:30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>16666.67</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/26 15:30:53</t>
+          <t>08/27 16:33:14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>266000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>31666.67</t>
+          <t>16666.67</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/23 09:56:14</t>
+          <t>08/26 15:30:53</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>266000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,12 +389,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>31666.67</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>马书文</t>
+          <t/>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/12 14:48:22</t>
+          <t>08/23 09:56:14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,17 +426,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>姚治文</t>
+          <t>马书文</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/11 14:11:24</t>
+          <t>08/12 14:48:22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,12 +473,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10843.37</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>姚治文</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/07 13:37:02</t>
+          <t>08/11 14:11:24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,17 +515,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>10843.37</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/04 13:42:31</t>
+          <t>08/07 13:37:02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/27 15:17:33</t>
+          <t>08/04 13:42:31</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,17 +594,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10714.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/27 11:23:18</t>
+          <t>07/27 15:17:33</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>215000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,22 +636,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>25903.61</t>
+          <t>10714.29</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/24 11:11:31</t>
+          <t>07/27 11:23:18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>215000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,17 +683,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>25903.61</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>卢华</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/15 13:16:56</t>
+          <t>07/24 11:11:31</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,22 +720,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>邓迎春</t>
+          <t>卢华</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,166 +747,181 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>07/15 13:16:56</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>10588.24</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>邓迎春</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>07/07 10:57:55</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>58823.53</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>张黎</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/03 15:50:47</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/03 14:06:24</t>
+          <t>09/03 15:50:47</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -928,12 +943,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>09/03 14:06:24</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -955,12 +970,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -982,12 +997,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -997,7 +1012,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1009,12 +1024,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1036,12 +1051,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1063,12 +1078,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1078,7 +1093,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1090,12 +1105,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1117,12 +1132,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1144,12 +1159,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1171,12 +1186,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1198,12 +1213,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1225,12 +1240,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1252,12 +1267,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1279,12 +1294,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1306,12 +1321,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1333,12 +1348,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1348,7 +1363,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1360,12 +1375,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1387,83 +1402,110 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="48"/>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2511000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>299231.01</t>
+          <t>2581000</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>312071</t>
+          <t>307767.59</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>312071</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>-12839.99</t>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>-4303.41</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -916,12 +916,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/03 15:50:47</t>
+          <t>09/04 18:27:05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -943,12 +943,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/03 14:06:24</t>
+          <t>09/03 15:50:47</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -970,12 +970,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>09/03 14:06:24</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1024,12 +1024,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1051,12 +1051,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1078,12 +1078,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1105,12 +1105,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1132,12 +1132,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1159,12 +1159,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1186,12 +1186,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1213,12 +1213,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1240,12 +1240,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1267,12 +1267,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1294,12 +1294,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1321,12 +1321,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1348,12 +1348,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1375,12 +1375,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1402,12 +1402,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1429,83 +1429,110 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="49"/>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="50"/>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2581000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>307767.59</t>
+          <t>2581000</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>312071</t>
+          <t>307767.59</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>320607</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>-4303.41</t>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>-12839.41</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/04 17:04:18</t>
+          <t>09/05 16:45:49</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8536.59</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/03 14:05:04</t>
+          <t>09/04 17:04:18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,22 +132,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11627.91</t>
+          <t>8536.59</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>贾凌</t>
+          <t>唐志刚</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/03 12:12:00</t>
+          <t>09/03 14:05:04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>95000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,22 +174,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11309.52</t>
+          <t>11627.91</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>毕春丽</t>
+          <t>贾凌</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/02 15:56:24</t>
+          <t>09/03 12:12:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>95000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,22 +216,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>9036.14</t>
+          <t>11309.52</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>许定勇</t>
+          <t>毕春丽</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/30 10:19:15</t>
+          <t>09/02 15:56:24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,22 +258,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>9036.14</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>胡琪斌</t>
+          <t>许定勇</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/28 11:17:30</t>
+          <t>08/30 10:19:15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,12 +305,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t/>
+          <t>胡琪斌</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/27 16:33:14</t>
+          <t>08/28 11:17:30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>16666.67</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/26 15:30:53</t>
+          <t>08/27 16:33:14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>266000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>31666.67</t>
+          <t>16666.67</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/23 09:56:14</t>
+          <t>08/26 15:30:53</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>266000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,12 +431,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>31666.67</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>马书文</t>
+          <t/>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/12 14:48:22</t>
+          <t>08/23 09:56:14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,17 +468,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>姚治文</t>
+          <t>马书文</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/11 14:11:24</t>
+          <t>08/12 14:48:22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,12 +515,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>10843.37</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>姚治文</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/07 13:37:02</t>
+          <t>08/11 14:11:24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,17 +557,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>10843.37</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/04 13:42:31</t>
+          <t>08/07 13:37:02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/27 15:17:33</t>
+          <t>08/04 13:42:31</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,17 +636,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>10714.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/27 11:23:18</t>
+          <t>07/27 15:17:33</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>215000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,22 +678,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>25903.61</t>
+          <t>10714.29</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/24 11:11:31</t>
+          <t>07/27 11:23:18</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>215000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,17 +725,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>25903.61</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>卢华</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/15 13:16:56</t>
+          <t>07/24 11:11:31</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,22 +762,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>邓迎春</t>
+          <t>卢华</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,166 +789,181 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>07/15 13:16:56</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>10588.24</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>邓迎春</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>07/07 10:57:55</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>58823.53</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>张黎</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/04 18:27:05</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/03 15:50:47</t>
+          <t>09/04 18:27:05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -970,12 +985,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/03 14:06:24</t>
+          <t>09/03 15:50:47</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -997,12 +1012,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>09/03 14:06:24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1024,12 +1039,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1051,12 +1066,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1066,7 +1081,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1078,12 +1093,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1105,12 +1120,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1132,12 +1147,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1147,7 +1162,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1159,12 +1174,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1186,12 +1201,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1213,12 +1228,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1240,12 +1255,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1267,12 +1282,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1294,12 +1309,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1321,12 +1336,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1348,12 +1363,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1375,12 +1390,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1402,12 +1417,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1417,7 +1432,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1429,12 +1444,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1456,83 +1471,110 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="50"/>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2581000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>307767.59</t>
+          <t>2631000</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>320607</t>
+          <t>313865.15</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>320607</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>-12839.41</t>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>-6741.85</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -958,12 +958,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/04 18:27:05</t>
+          <t>09/05 18:36:53</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -985,12 +985,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/03 15:50:47</t>
+          <t>09/04 18:27:05</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1012,12 +1012,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/03 14:06:24</t>
+          <t>09/03 15:50:47</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1039,12 +1039,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>09/03 14:06:24</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1066,12 +1066,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1093,12 +1093,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1120,12 +1120,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1147,12 +1147,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1174,12 +1174,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1201,12 +1201,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1228,12 +1228,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1255,12 +1255,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1282,12 +1282,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1309,12 +1309,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1336,12 +1336,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1363,12 +1363,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1390,12 +1390,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1417,12 +1417,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1444,12 +1444,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1471,12 +1471,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1498,83 +1498,110 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="51"/>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2631000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>313865.15</t>
+          <t>2631000</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>320607</t>
+          <t>313865.15</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>326704</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>-6741.85</t>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>-12838.85</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/05 16:45:49</t>
+          <t>09/08 12:06:24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,17 +90,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>唐志刚</t>
+          <t/>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/04 17:04:18</t>
+          <t>09/05 16:45:49</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8536.59</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/03 14:05:04</t>
+          <t>09/04 17:04:18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,22 +174,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11627.91</t>
+          <t>8536.59</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>贾凌</t>
+          <t>唐志刚</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/03 12:12:00</t>
+          <t>09/03 14:05:04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>95000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,22 +216,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11309.52</t>
+          <t>11627.91</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>毕春丽</t>
+          <t>贾凌</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/02 15:56:24</t>
+          <t>09/03 12:12:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>95000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,22 +258,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>9036.14</t>
+          <t>11309.52</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>许定勇</t>
+          <t>毕春丽</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/30 10:19:15</t>
+          <t>09/02 15:56:24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,22 +300,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>9036.14</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>胡琪斌</t>
+          <t>许定勇</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/28 11:17:30</t>
+          <t>08/30 10:19:15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,12 +347,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t/>
+          <t>胡琪斌</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/27 16:33:14</t>
+          <t>08/28 11:17:30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>16666.67</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/26 15:30:53</t>
+          <t>08/27 16:33:14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>266000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>31666.67</t>
+          <t>16666.67</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/23 09:56:14</t>
+          <t>08/26 15:30:53</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>266000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,12 +473,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>31666.67</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>马书文</t>
+          <t/>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/12 14:48:22</t>
+          <t>08/23 09:56:14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,17 +510,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>姚治文</t>
+          <t>马书文</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/11 14:11:24</t>
+          <t>08/12 14:48:22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,12 +557,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10843.37</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>姚治文</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/07 13:37:02</t>
+          <t>08/11 14:11:24</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,17 +599,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>10843.37</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/04 13:42:31</t>
+          <t>08/07 13:37:02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/27 15:17:33</t>
+          <t>08/04 13:42:31</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,17 +678,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>10714.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/27 11:23:18</t>
+          <t>07/27 15:17:33</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>215000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,22 +720,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>25903.61</t>
+          <t>10714.29</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/24 11:11:31</t>
+          <t>07/27 11:23:18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>215000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,17 +767,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>25903.61</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>卢华</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/15 13:16:56</t>
+          <t>07/24 11:11:31</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,22 +804,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>邓迎春</t>
+          <t>卢华</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,166 +831,181 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>07/15 13:16:56</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>10588.24</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>邓迎春</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>07/07 10:57:55</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>58823.53</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>张黎</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/05 18:36:53</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/04 18:27:05</t>
+          <t>09/05 18:36:53</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1012,12 +1027,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/03 15:50:47</t>
+          <t>09/04 18:27:05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1039,12 +1054,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/03 14:06:24</t>
+          <t>09/03 15:50:47</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1066,12 +1081,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>09/03 14:06:24</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1093,12 +1108,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1120,12 +1135,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1135,7 +1150,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1147,12 +1162,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1174,12 +1189,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1201,12 +1216,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1216,7 +1231,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1228,12 +1243,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1255,12 +1270,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1282,12 +1297,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1309,12 +1324,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1336,12 +1351,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1363,12 +1378,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1390,12 +1405,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1417,12 +1432,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1444,12 +1459,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1471,12 +1486,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1486,7 +1501,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1498,12 +1513,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1525,83 +1540,110 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="52"/>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="53"/>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2631000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>313865.15</t>
+          <t>2731000</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>326704</t>
+          <t>325769.92</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>326704</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>-12838.85</t>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>-934.08</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -1000,12 +1000,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/05 18:36:53</t>
+          <t>09/08 15:08:10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1027,12 +1027,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/04 18:27:05</t>
+          <t>09/05 18:36:53</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1054,12 +1054,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/03 15:50:47</t>
+          <t>09/04 18:27:05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1081,12 +1081,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/03 14:06:24</t>
+          <t>09/03 15:50:47</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1108,12 +1108,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>09/03 14:06:24</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1135,12 +1135,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1162,12 +1162,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1189,12 +1189,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1243,12 +1243,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1270,12 +1270,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1297,12 +1297,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1324,12 +1324,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1351,12 +1351,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1378,12 +1378,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1405,12 +1405,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1432,12 +1432,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1486,12 +1486,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1513,12 +1513,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1540,12 +1540,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1567,83 +1567,110 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="53"/>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2731000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>325769.92</t>
+          <t>2731000</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>326704</t>
+          <t>325769.92</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>338608</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>-934.08</t>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>-12838.08</t>
         </is>
       </c>
     </row>
